--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEW_MEXICO_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/NEW_MEXICO_2017.xlsx
@@ -445,7 +445,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="6">
@@ -1597,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="D69">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="70">
@@ -1885,7 +1885,7 @@
         <v>8</v>
       </c>
       <c r="D85">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="86">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C117">
@@ -2623,7 +2623,7 @@
         <v>8</v>
       </c>
       <c r="D126">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="127">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C159">
@@ -3541,7 +3541,7 @@
         <v>8</v>
       </c>
       <c r="D177">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="178">
@@ -3631,7 +3631,7 @@
         <v>8</v>
       </c>
       <c r="D182">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="183">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C248">
@@ -6619,7 +6619,7 @@
         <v>8</v>
       </c>
       <c r="D348">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="349">
@@ -7051,7 +7051,7 @@
         <v>82</v>
       </c>
       <c r="D372">
-        <v>0.009264489888148231</v>
+        <v>0.009264489888148233</v>
       </c>
     </row>
     <row r="373">
@@ -9625,7 +9625,7 @@
         <v>8</v>
       </c>
       <c r="D515">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="516">
@@ -9985,7 +9985,7 @@
         <v>8</v>
       </c>
       <c r="D535">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="536">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C551">
@@ -11425,7 +11425,7 @@
         <v>8</v>
       </c>
       <c r="D615">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="616">
@@ -12217,7 +12217,7 @@
         <v>8</v>
       </c>
       <c r="D659">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="660">
@@ -12613,7 +12613,7 @@
         <v>8</v>
       </c>
       <c r="D681">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="682">
@@ -12937,7 +12937,7 @@
         <v>8</v>
       </c>
       <c r="D699">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="700">
@@ -13477,7 +13477,7 @@
         <v>8</v>
       </c>
       <c r="D729">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="730">
@@ -13729,7 +13729,7 @@
         <v>8</v>
       </c>
       <c r="D743">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="744">
@@ -13999,7 +13999,7 @@
         <v>8</v>
       </c>
       <c r="D758">
-        <v>0.0009038526720144617</v>
+        <v>0.0009038526720144616</v>
       </c>
     </row>
     <row r="759">
